--- a/data/leads_final.xlsx
+++ b/data/leads_final.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Lead Listesi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lead Listesi'!$A$1:$Y$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lead Listesi'!$A$1:$S$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y182"/>
+  <dimension ref="A1:S182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -450,12 +450,6 @@
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="60" customWidth="1" min="24" max="24"/>
-    <col width="45" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,36 +548,6 @@
           <t>Email Güven Skoru</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Email Kanit URL</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Email Kaynak</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Email Pattern</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Email Notlari</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Email Arama Sorgulari</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Email Bulunan URL</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -669,36 +633,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>https://www.trendyol.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Company contact page uses @trendyol.com domain</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>"Yasin Selim Yandik" "Trendyol" email || "Yasin Selim Yandik" "@trendyol.com" || site:trendyol.com "yasin.yandik" || site:trendyol.com "@trendyol.com" || "Trendyol" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://www.trendyol.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -784,36 +718,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>"Nurullah Er" "Turkcell" email || "Nurullah Er" "@turkcell.com.tr" || site:turkcell.com.tr "nurullah.er" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -899,36 +803,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>"Ahmet Diril" "Turkcell" email || "Ahmet Diril" "@turkcell.com.tr" || site:turkcell.com.tr "ahmet.diril" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1014,36 +888,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>"Pelin Anil" "Turkcell" email || "Pelin Anil" "@turkcell.com.tr" || site:turkcell.com.tr "pelin.anil" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1129,36 +973,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>"Fatma Pınar Mutlu" "Turkcell" email || "Fatma Pınar Mutlu" "@turkcell.com.tr" || site:turkcell.com.tr "fatma.mutlu" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1244,36 +1058,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>"Nazan Kıroğlu" "Turkcell" email || "Nazan Kıroğlu" "@turkcell.com.tr" || site:turkcell.com.tr "nazan.kiroglu" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1359,36 +1143,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>"Su Karagöz Bozoğlu" "Turkcell" email || "Su Karagöz Bozoğlu" "@turkcell.com.tr" || site:turkcell.com.tr "su.bozoglu" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1474,36 +1228,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Company PDF confirms @turkcell.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>"Şerife Seda Kaya" "Turkcell" email || "Şerife Seda Kaya" "@turkcell.com.tr" || site:turkcell.com.tr "serife.kaya" || site:turkcell.com.tr "@turkcell.com.tr" || "Turkcell" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://tedarik.turkcell.com.tr/Shared%20Documents/BeSupplier/TURKCELL%20%C4%B0NSAN%20HAKLARI%20POL%C4%B0T%C4%B0KASI.pdf</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1589,36 +1313,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>"Ayten Cerrah" "Koç Holding" email || "Ayten Cerrah" "@koc.com.tr" || site:koc.com.tr "ayten.cerrah" || site:koc.com.tr "@koc.com.tr" || "Koç Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1704,36 +1398,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>"Enes Külçe" "Koç Holding" email || "Enes Külçe" "@koc.com.tr" || site:koc.com.tr "enes.kulce" || site:koc.com.tr "@koc.com.tr" || "Koç Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1819,36 +1483,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>"Eli̇f Kaplan" "Koç Holding" email || "Eli̇f Kaplan" "@koc.com.tr" || site:koc.com.tr "elif.kaplan" || site:koc.com.tr "@koc.com.tr" || "Koç Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1934,36 +1568,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>"Asena Akbalcılar Aşkın" "Koç Holding" email || "Asena Akbalcılar Aşkın" "@koc.com.tr" || site:koc.com.tr "asena.askin" || site:koc.com.tr "@koc.com.tr" || "Koç Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2049,36 +1653,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>"Nilay Bölükbaşı" "Koç Holding" email || "Nilay Bölükbaşı" "@koc.com.tr" || site:koc.com.tr "nilay.bolukbasi" || site:koc.com.tr "@koc.com.tr" || "Koç Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://www.koc.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2164,36 +1738,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>https://www.sabanci.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>"Gurhan Kurukahveciler" "Sabancı Holding" email || "Gurhan Kurukahveciler" "@sabanci.com" || site:sabanci.com "gurhan.kurukahveciler" || site:sabanci.com "@sabanci.com" || "Sabancı Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://www.sabanci.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2279,36 +1823,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>https://www.garantibbva.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>"Pinar Aktug" "Garanti BBVA" email || "Pinar Aktug" "@garantibbva.com.tr" || site:garantibbva.com.tr "pinar.aktug" || site:garantibbva.com.tr "@garantibbva.com.tr" || "Garanti BBVA" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://www.garantibbva.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2394,36 +1908,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>"Şengül Kösem" "İş Bankası" email || "Şengül Kösem" "@isbank.com.tr" || site:isbank.com.tr "sengul.kosem" || site:isbank.com.tr "@isbank.com.tr" || "İş Bankası" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2509,36 +1993,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>"Hakan Torun" "İş Bankası" email || "Hakan Torun" "@isbank.com.tr" || site:isbank.com.tr "hakan.torun" || site:isbank.com.tr "@isbank.com.tr" || "İş Bankası" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2624,36 +2078,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>"Ali Yalçın" "İş Bankası" email || "Ali Yalçın" "@isbank.com.tr" || site:isbank.com.tr "ali.yalcin" || site:isbank.com.tr "@isbank.com.tr" || "İş Bankası" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2739,36 +2163,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>"Ceren Kapılı" "İş Bankası" email || "Ceren Kapılı" "@isbank.com.tr" || site:isbank.com.tr "ceren.kapili" || site:isbank.com.tr "@isbank.com.tr" || "İş Bankası" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2854,36 +2248,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>"Seda Tuğut" "İş Bankası" email || "Seda Tuğut" "@isbank.com.tr" || site:isbank.com.tr "seda.tugut" || site:isbank.com.tr "@isbank.com.tr" || "İş Bankası" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://www.isbank.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2969,36 +2333,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>"Emre Gökduman" "Akbank" email || "Emre Gökduman" "@akbank.com" || site:akbank.com "emre.gokduman" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3084,36 +2418,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>"Işik Akgül" "Akbank" email || "Işik Akgül" "@akbank.com" || site:akbank.com "isik.akgul" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3199,36 +2503,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>"Serdal Çavuş" "Akbank" email || "Serdal Çavuş" "@akbank.com" || site:akbank.com "serdal.cavus" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3314,36 +2588,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>"Gamze Kuzu" "Akbank" email || "Gamze Kuzu" "@akbank.com" || site:akbank.com "gamze.kuzu" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3429,36 +2673,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>"Fatma Yeşim Bozkurt" "Akbank" email || "Fatma Yeşim Bozkurt" "@akbank.com" || site:akbank.com "fatma.bozkurt" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3544,36 +2758,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>"Humeyra Cevik" "Akbank" email || "Humeyra Cevik" "@akbank.com" || site:akbank.com "humeyra.cevik" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3659,36 +2843,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>"Sibel Sungur" "Akbank" email || "Sibel Sungur" "@akbank.com" || site:akbank.com "sibel.sungur" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3774,36 +2928,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>"Ayça Bahar Demir" "Akbank" email || "Ayça Bahar Demir" "@akbank.com" || site:akbank.com "ayca.demir" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3889,36 +3013,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Bank contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>"Pelin Baran" "Akbank" email || "Pelin Baran" "@akbank.com" || site:akbank.com "pelin.baran" || site:akbank.com "@akbank.com" || "Akbank" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://www.akbank.com/tr-tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4004,36 +3098,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Company career page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>"Neslihan Ç." "Getir" email || "Neslihan Ç." "@getir.com" || site:getir.com "neslihan.c" || site:getir.com "@getir.com" || "Getir" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4119,36 +3183,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Company career page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>"Eda Ozpoyraz" "Getir" email || "Eda Ozpoyraz" "@getir.com" || site:getir.com "eda.ozpoyraz" || site:getir.com "@getir.com" || "Getir" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4234,36 +3268,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Company career page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>"Emrah Ayyıldız" "Getir" email || "Emrah Ayyıldız" "@getir.com" || site:getir.com "emrah.ayyildiz" || site:getir.com "@getir.com" || "Getir" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4349,36 +3353,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Company career page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>"Başak Evrim Daltaban" "Getir" email || "Başak Evrim Daltaban" "@getir.com" || site:getir.com "basak.daltaban" || site:getir.com "@getir.com" || "Getir" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>https://getir.com/tr/kariyer/</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4464,36 +3438,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>https://www.hepsiburada.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>"Vildan Akar" "Hepsiburada" email || "Vildan Akar" "@hepsiburada.com" || site:hepsiburada.com "vildan.akar" || site:hepsiburada.com "@hepsiburada.com" || "Hepsiburada" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>https://www.hepsiburada.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4579,36 +3523,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>https://www.hepsiburada.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>"Ayça Çelik Ilındır" "Hepsiburada" email || "Ayça Çelik Ilındır" "@hepsiburada.com" || site:hepsiburada.com "ayca.ilindir" || site:hepsiburada.com "@hepsiburada.com" || "Hepsiburada" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://www.hepsiburada.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4694,36 +3608,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>"Ayşemelek Altınbağ" "Arçelik" email || "Ayşemelek Altınbağ" "@arcelik.com" || site:arcelik.com "aysemelek.altinbag" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4809,36 +3693,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>"Ülkü Hızlı" "Arçelik" email || "Ülkü Hızlı" "@arcelik.com" || site:arcelik.com "ulku.hizli" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4924,36 +3778,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>"Ilknur Serdar" "Arçelik" email || "Ilknur Serdar" "@arcelik.com" || site:arcelik.com "ilknur.serdar" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5039,36 +3863,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>"Serdar Ölmez" "Arçelik" email || "Serdar Ölmez" "@arcelik.com" || site:arcelik.com "serdar.olmez" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5154,36 +3948,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>"Ali Orhan" "Arçelik" email || "Ali Orhan" "@arcelik.com" || site:arcelik.com "ali.orhan" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5269,36 +4033,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>"Mücahid Yıldırım" "Arçelik" email || "Mücahid Yıldırım" "@arcelik.com" || site:arcelik.com "mucahid.yildirim" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5384,36 +4118,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>"Kader Çetinkaya Yılmaz" "Arçelik" email || "Kader Çetinkaya Yılmaz" "@arcelik.com" || site:arcelik.com "kader.yilmaz" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5499,36 +4203,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>"Özge Şahin" "Arçelik" email || "Özge Şahin" "@arcelik.com" || site:arcelik.com "ozge.sahin" || site:arcelik.com "@arcelik.com" || "Arçelik" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>https://www.arcelik.com/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5614,36 +4288,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>"Bahattin Aydın" "LC Waikiki" email || "Bahattin Aydın" "@lcwaikiki.com" || site:lcwaikiki.com "bahattin.aydin" || site:lcwaikiki.com "@lcwaikiki.com" || "LC Waikiki" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5729,36 +4373,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>"Nilufer Bozkurt" "LC Waikiki" email || "Nilufer Bozkurt" "@lcwaikiki.com" || site:lcwaikiki.com "nilufer.bozkurt" || site:lcwaikiki.com "@lcwaikiki.com" || "LC Waikiki" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5844,36 +4458,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>"Özge Başıbüyük" "LC Waikiki" email || "Özge Başıbüyük" "@lcwaikiki.com" || site:lcwaikiki.com "ozge.basibuyuk" || site:lcwaikiki.com "@lcwaikiki.com" || "LC Waikiki" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5959,36 +4543,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>"Satiye Akpinar" "LC Waikiki" email || "Satiye Akpinar" "@lcwaikiki.com" || site:lcwaikiki.com "satiye.akpinar" || site:lcwaikiki.com "@lcwaikiki.com" || "LC Waikiki" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6074,36 +4628,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>"Özgül Emre" "LC Waikiki" email || "Özgül Emre" "@lcwaikiki.com" || site:lcwaikiki.com "ozgul.emre" || site:lcwaikiki.com "@lcwaikiki.com" || "LC Waikiki" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6189,36 +4713,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>"Tuğba Mavi" "LC Waikiki" email || "Tuğba Mavi" "@lcwaikiki.com" || site:lcwaikiki.com "tugba.mavi" || site:lcwaikiki.com "@lcwaikiki.com" || "LC Waikiki" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>https://www.lcwaikiki.com/tr-TR/TR/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6304,36 +4798,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>"Begüm Tekin" "Migros" email || "Begüm Tekin" "@migros.com.tr" || site:migros.com.tr "begum.tekin" || site:migros.com.tr "@migros.com.tr" || "Migros" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6419,36 +4883,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>"Öznur Kaya" "Migros" email || "Öznur Kaya" "@migros.com.tr" || site:migros.com.tr "oznur.kaya" || site:migros.com.tr "@migros.com.tr" || "Migros" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6534,36 +4968,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>"Yağmur Çetin" "Migros" email || "Yağmur Çetin" "@migros.com.tr" || site:migros.com.tr "yagmur.cetin" || site:migros.com.tr "@migros.com.tr" || "Migros" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6649,36 +5053,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>"Olcay Yılmaz Nomak" "Migros" email || "Olcay Yılmaz Nomak" "@migros.com.tr" || site:migros.com.tr "olcay.nomak" || site:migros.com.tr "@migros.com.tr" || "Migros" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6764,36 +5138,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>"Özkan Birlik" "Migros" email || "Özkan Birlik" "@migros.com.tr" || site:migros.com.tr "ozkan.birlik" || site:migros.com.tr "@migros.com.tr" || "Migros" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>https://www.migros.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6879,36 +5223,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>"Hasan Kaya" "BİM" email || "Hasan Kaya" "@bim.com.tr" || site:bim.com.tr "hasan.kaya" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6994,36 +5308,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>"Elif Sağdıç" "BİM" email || "Elif Sağdıç" "@bim.com.tr" || site:bim.com.tr "elif.sagdic" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7109,36 +5393,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>"Muhammed Furkan Kar" "BİM" email || "Muhammed Furkan Kar" "@bim.com.tr" || site:bim.com.tr "muhammed.kar" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7224,36 +5478,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>"Arife Özgül" "BİM" email || "Arife Özgül" "@bim.com.tr" || site:bim.com.tr "arife.ozgul" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7339,36 +5563,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>"Ebru Kuru" "BİM" email || "Ebru Kuru" "@bim.com.tr" || site:bim.com.tr "ebru.kuru" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7454,36 +5648,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>"Arda Baştimur" "BİM" email || "Arda Baştimur" "@bim.com.tr" || site:bim.com.tr "arda.bastimur" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7569,36 +5733,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>"Mutlu Önder" "BİM" email || "Mutlu Önder" "@bim.com.tr" || site:bim.com.tr "mutlu.onder" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7684,36 +5818,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>"Berke Şaşkın" "BİM" email || "Berke Şaşkın" "@bim.com.tr" || site:bim.com.tr "berke.saskin" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7799,36 +5903,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>"Hilal Oktar" "BİM" email || "Hilal Oktar" "@bim.com.tr" || site:bim.com.tr "hilal.oktar" || site:bim.com.tr "@bim.com.tr" || "BİM" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>https://www.bim.com.tr/iletisim.aspx</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7914,36 +5988,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Investor relations contact page — @thy.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>"Merve İzol Selçuk" "THY" email || "Merve İzol Selçuk" "@thy.com" || site:thy.com "merve.selcuk" || site:thy.com "@thy.com" || "THY" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8029,36 +6073,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Investor relations contact page — @thy.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>"Metin Elmas" "THY" email || "Metin Elmas" "@thy.com" || site:thy.com "metin.elmas" || site:thy.com "@thy.com" || "THY" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8144,36 +6158,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Investor relations contact page — @thy.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>"Pelin Erel" "THY" email || "Pelin Erel" "@thy.com" || site:thy.com "pelin.erel" || site:thy.com "@thy.com" || "THY" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8259,36 +6243,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Investor relations contact page — @thy.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>"Büşra Özel" "THY" email || "Büşra Özel" "@thy.com" || site:thy.com "busra.ozel" || site:thy.com "@thy.com" || "THY" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8374,36 +6328,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Investor relations contact page — @thy.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>"Muhammed Yusuf Sarıoğlu" "THY" email || "Muhammed Yusuf Sarıoğlu" "@thy.com" || site:thy.com "muhammed.sarioglu" || site:thy.com "@thy.com" || "THY" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>https://investor.thy.com/tr/contact</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8489,36 +6413,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>https://www.flypgs.com/kurumsal/iletisim</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>"Ersin S." "Pegasus" email || "Ersin S." "@flypgs.com" || site:flypgs.com "ersin.s" || site:flypgs.com "@flypgs.com" || "Pegasus" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>https://www.flypgs.com/kurumsal/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8604,36 +6498,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>https://www.flypgs.com/kurumsal/iletisim</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>"Yeliz Doğan" "Pegasus" email || "Yeliz Doğan" "@flypgs.com" || site:flypgs.com "yeliz.dogan" || site:flypgs.com "@flypgs.com" || "Pegasus" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>https://www.flypgs.com/kurumsal/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8719,36 +6583,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>https://www.flypgs.com/kurumsal/iletisim</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>"Fulya Altinkayak" "Pegasus" email || "Fulya Altinkayak" "@flypgs.com" || site:flypgs.com "fulya.altinkayak" || site:flypgs.com "@flypgs.com" || "Pegasus" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>https://www.flypgs.com/kurumsal/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8834,36 +6668,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>https://www.vodafone.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>"Nazlı Tlabar Güler" "Vodafone Turkey" email || "Nazlı Tlabar Güler" "@vodafone.com.tr" || site:vodafone.com.tr "nazli.guler" || site:vodafone.com.tr "@vodafone.com.tr" || "Vodafone Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>https://www.vodafone.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8949,36 +6753,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>https://www.vodafone.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>"Serdar Akcay" "Vodafone Turkey" email || "Serdar Akcay" "@vodafone.com.tr" || site:vodafone.com.tr "serdar.akcay" || site:vodafone.com.tr "@vodafone.com.tr" || "Vodafone Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>https://www.vodafone.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9064,36 +6838,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>https://www.vodafone.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>"Senem Palabiyik" "Vodafone Turkey" email || "Senem Palabiyik" "@vodafone.com.tr" || site:vodafone.com.tr "senem.palabiyik" || site:vodafone.com.tr "@vodafone.com.tr" || "Vodafone Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>https://www.vodafone.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9179,36 +6923,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Multinational — pg.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>"Banu Yıldırım" "P&amp;G Turkey" email || "Banu Yıldırım" "@pg.com" || site:pg.com "banu.yildirim" || site:pg.com "@pg.com" || "P&amp;G Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9294,36 +7008,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Multinational — pg.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>"Kardelen Kaya" "P&amp;G Turkey" email || "Kardelen Kaya" "@pg.com" || site:pg.com "kardelen.kaya" || site:pg.com "@pg.com" || "P&amp;G Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9409,36 +7093,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Multinational — pg.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>"Mustafa Isliyen" "P&amp;G Turkey" email || "Mustafa Isliyen" "@pg.com" || site:pg.com "mustafa.isliyen" || site:pg.com "@pg.com" || "P&amp;G Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9524,36 +7178,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Multinational — pg.com domain confirmed</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>"Yesim Ertem" "P&amp;G Turkey" email || "Yesim Ertem" "@pg.com" || site:pg.com "yesim.ertem" || site:pg.com "@pg.com" || "P&amp;G Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>https://www.pg.com/tr_TR/contact</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9639,36 +7263,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>"Ersin Yılmaz" "Şişecam" email || "Ersin Yılmaz" "@sisecam.com" || site:sisecam.com "ersin.yilmaz" || site:sisecam.com "@sisecam.com" || "Şişecam" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9754,36 +7348,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>"Neslihan Ünal" "Şişecam" email || "Neslihan Ünal" "@sisecam.com" || site:sisecam.com "neslihan.unal" || site:sisecam.com "@sisecam.com" || "Şişecam" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9869,36 +7433,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>"Serhat Akinci" "Şişecam" email || "Serhat Akinci" "@sisecam.com" || site:sisecam.com "serhat.akinci" || site:sisecam.com "@sisecam.com" || "Şişecam" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9984,36 +7518,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>"Cihan U." "Şişecam" email || "Cihan U." "@sisecam.com" || site:sisecam.com "cihan.u" || site:sisecam.com "@sisecam.com" || "Şişecam" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10099,36 +7603,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>"Özgür Altun" "Şişecam" email || "Özgür Altun" "@sisecam.com" || site:sisecam.com "ozgur.altun" || site:sisecam.com "@sisecam.com" || "Şişecam" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10214,36 +7688,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Corporate contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>"Erhan Ay" "Şişecam" email || "Erhan Ay" "@sisecam.com" || site:sisecam.com "erhan.ay" || site:sisecam.com "@sisecam.com" || "Şişecam" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>https://www.sisecam.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10329,36 +7773,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>https://www.fordotosan.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>"Eda Pak" "Ford Otosan" email || "Eda Pak" "@fordotosan.com.tr" || site:fordotosan.com.tr "eda.pak" || site:fordotosan.com.tr "@fordotosan.com.tr" || "Ford Otosan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>https://www.fordotosan.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10444,36 +7858,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>https://www.fordotosan.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>"İsmail Öztürk" "Ford Otosan" email || "İsmail Öztürk" "@fordotosan.com.tr" || site:fordotosan.com.tr "ismail.ozturk" || site:fordotosan.com.tr "@fordotosan.com.tr" || "Ford Otosan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>https://www.fordotosan.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10559,36 +7943,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>https://www.fordotosan.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>"Ecem Kirgec Akman" "Ford Otosan" email || "Ecem Kirgec Akman" "@fordotosan.com.tr" || site:fordotosan.com.tr "ecem.akman" || site:fordotosan.com.tr "@fordotosan.com.tr" || "Ford Otosan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>https://www.fordotosan.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10674,36 +8028,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>"Necdet Pek" "Tofaş" email || "Necdet Pek" "@tofas.com.tr" || site:tofas.com.tr "necdet.pek" || site:tofas.com.tr "@tofas.com.tr" || "Tofaş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10789,36 +8113,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>"Ertan Şentürk" "Tofaş" email || "Ertan Şentürk" "@tofas.com.tr" || site:tofas.com.tr "ertan.senturk" || site:tofas.com.tr "@tofas.com.tr" || "Tofaş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10904,36 +8198,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>"Engin Kahraman" "Tofaş" email || "Engin Kahraman" "@tofas.com.tr" || site:tofas.com.tr "engin.kahraman" || site:tofas.com.tr "@tofas.com.tr" || "Tofaş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11019,36 +8283,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>"Mine Kahraman" "Tofaş" email || "Mine Kahraman" "@tofas.com.tr" || site:tofas.com.tr "mine.kahraman" || site:tofas.com.tr "@tofas.com.tr" || "Tofaş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11134,36 +8368,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>"Elif Işık Akpınar" "Tofaş" email || "Elif Işık Akpınar" "@tofas.com.tr" || site:tofas.com.tr "elif.akpinar" || site:tofas.com.tr "@tofas.com.tr" || "Tofaş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11249,36 +8453,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Automotive contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>"Emel Mert Büyükçakmak" "Tofaş" email || "Emel Mert Büyükçakmak" "@tofas.com.tr" || site:tofas.com.tr "emel.buyukcakmak" || site:tofas.com.tr "@tofas.com.tr" || "Tofaş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>https://www.tofas.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11364,36 +8538,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>"Murat Akbulut" "Eczacıbaşı" email || "Murat Akbulut" "@eczacibasi.com.tr" || site:eczacibasi.com.tr "murat.akbulut" || site:eczacibasi.com.tr "@eczacibasi.com.tr" || "Eczacıbaşı" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11479,36 +8623,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>"Öznur Plana" "Eczacıbaşı" email || "Öznur Plana" "@eczacibasi.com.tr" || site:eczacibasi.com.tr "oznur.plana" || site:eczacibasi.com.tr "@eczacibasi.com.tr" || "Eczacıbaşı" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11594,36 +8708,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>"Serdar S." "Eczacıbaşı" email || "Serdar S." "@eczacibasi.com.tr" || site:eczacibasi.com.tr "serdar.s" || site:eczacibasi.com.tr "@eczacibasi.com.tr" || "Eczacıbaşı" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11709,36 +8793,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>"Yıldırım Şimşek" "Eczacıbaşı" email || "Yıldırım Şimşek" "@eczacibasi.com.tr" || site:eczacibasi.com.tr "yildirim.simsek" || site:eczacibasi.com.tr "@eczacibasi.com.tr" || "Eczacıbaşı" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>https://www.eczacibasi.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11824,36 +8878,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>"Adem Öztürk" "Türk Telekom" email || "Adem Öztürk" "@turktelekom.com.tr" || site:turktelekom.com.tr "adem.ozturk" || site:turktelekom.com.tr "@turktelekom.com.tr" || "Türk Telekom" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11939,36 +8963,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>"Gülay Kurt" "Türk Telekom" email || "Gülay Kurt" "@turktelekom.com.tr" || site:turktelekom.com.tr "gulay.kurt" || site:turktelekom.com.tr "@turktelekom.com.tr" || "Türk Telekom" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12054,36 +9048,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>"Gökşen Afşar" "Türk Telekom" email || "Gökşen Afşar" "@turktelekom.com.tr" || site:turktelekom.com.tr "goksen.afsar" || site:turktelekom.com.tr "@turktelekom.com.tr" || "Türk Telekom" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12169,36 +9133,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>"Tuncay Dalgiç" "Türk Telekom" email || "Tuncay Dalgiç" "@turktelekom.com.tr" || site:turktelekom.com.tr "tuncay.dalgic" || site:turktelekom.com.tr "@turktelekom.com.tr" || "Türk Telekom" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12284,36 +9218,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Telecom contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>"Tamer Göze" "Türk Telekom" email || "Tamer Göze" "@turktelekom.com.tr" || site:turktelekom.com.tr "tamer.goze" || site:turktelekom.com.tr "@turktelekom.com.tr" || "Türk Telekom" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>https://www.turktelekom.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12399,36 +9303,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>"Ceren Aydın" "Enerjisa" email || "Ceren Aydın" "@enerjisa.com.tr" || site:enerjisa.com.tr "ceren.aydin" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12514,36 +9388,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>"Ümit Kuşlu" "Enerjisa" email || "Ümit Kuşlu" "@enerjisa.com.tr" || site:enerjisa.com.tr "umit.kuslu" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12629,36 +9473,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>"Eyüp Karaman" "Enerjisa" email || "Eyüp Karaman" "@enerjisa.com.tr" || site:enerjisa.com.tr "eyup.karaman" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12744,36 +9558,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>"Aysegul Gurkale" "Enerjisa" email || "Aysegul Gurkale" "@enerjisa.com.tr" || site:enerjisa.com.tr "aysegul.gurkale" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12859,36 +9643,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>"Seda Ö." "Enerjisa" email || "Seda Ö." "@enerjisa.com.tr" || site:enerjisa.com.tr "seda.o" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12974,36 +9728,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>"Burak Çeli̇k" "Enerjisa" email || "Burak Çeli̇k" "@enerjisa.com.tr" || site:enerjisa.com.tr "burak.celik" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13089,36 +9813,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Energy company contact page — domain confirmed</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>"Mehmet Karakoç" "Enerjisa" email || "Mehmet Karakoç" "@enerjisa.com.tr" || site:enerjisa.com.tr "mehmet.karakoc" || site:enerjisa.com.tr "@enerjisa.com.tr" || "Enerjisa" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>https://www.enerjisa.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13204,36 +9898,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>https://www.allianz.com.tr/tr_TR/sizin-icin/iletisim.html</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Insurance contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>"Özlem Yanmaz Ateş" "Allianz Turkey" email || "Özlem Yanmaz Ateş" "@allianz.com.tr" || site:allianz.com.tr "ozlem.ates" || site:allianz.com.tr "@allianz.com.tr" || "Allianz Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>https://www.allianz.com.tr/tr_TR/sizin-icin/iletisim.html</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13319,36 +9983,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>https://www.allianz.com.tr/tr_TR/sizin-icin/iletisim.html</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Insurance contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>"Volkan İnce" "Allianz Turkey" email || "Volkan İnce" "@allianz.com.tr" || site:allianz.com.tr "volkan.ince" || site:allianz.com.tr "@allianz.com.tr" || "Allianz Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>https://www.allianz.com.tr/tr_TR/sizin-icin/iletisim.html</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13434,36 +10068,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>https://www.allianz.com.tr/tr_TR/sizin-icin/iletisim.html</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Insurance contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>"Esra Kadıoğlu Dülger" "Allianz Turkey" email || "Esra Kadıoğlu Dülger" "@allianz.com.tr" || site:allianz.com.tr "esra.dulger" || site:allianz.com.tr "@allianz.com.tr" || "Allianz Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>https://www.allianz.com.tr/tr_TR/sizin-icin/iletisim.html</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13549,36 +10153,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>"Engin Ege" "Eti" email || "Engin Ege" "@eti.com.tr" || site:eti.com.tr "engin.ege" || site:eti.com.tr "@eti.com.tr" || "Eti" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13664,36 +10238,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>"Ahmet Hadimli" "Eti" email || "Ahmet Hadimli" "@eti.com.tr" || site:eti.com.tr "ahmet.hadimli" || site:eti.com.tr "@eti.com.tr" || "Eti" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13779,36 +10323,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>"Ümit Gürsoy" "Eti" email || "Ümit Gürsoy" "@eti.com.tr" || site:eti.com.tr "umit.gursoy" || site:eti.com.tr "@eti.com.tr" || "Eti" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13894,36 +10408,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>"Ayfer Aybatlı" "Eti" email || "Ayfer Aybatlı" "@eti.com.tr" || site:eti.com.tr "ayfer.aybatli" || site:eti.com.tr "@eti.com.tr" || "Eti" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14009,36 +10493,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>"Pelin Sümer" "Eti" email || "Pelin Sümer" "@eti.com.tr" || site:eti.com.tr "pelin.sumer" || site:eti.com.tr "@eti.com.tr" || "Eti" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14124,36 +10578,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>"Sedat Demirel" "Eti" email || "Sedat Demirel" "@eti.com.tr" || site:eti.com.tr "sedat.demirel" || site:eti.com.tr "@eti.com.tr" || "Eti" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>https://www.eti.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14239,36 +10663,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>https://www.ulker.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>"Ulker Day" "Ülker" email || "Ulker Day" "@ulker.com.tr" || site:ulker.com.tr "ulker.day" || site:ulker.com.tr "@ulker.com.tr" || "Ülker" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>https://www.ulker.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14354,36 +10748,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>https://www.ulker.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Food company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>"Meltem Ülker" "Ülker" email || "Meltem Ülker" "@ulker.com.tr" || site:ulker.com.tr "meltem.ulker" || site:ulker.com.tr "@ulker.com.tr" || "Ülker" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>https://www.ulker.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14469,36 +10833,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>Airport operator contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>"Sevil Arık" "TAV" email || "Sevil Arık" "@tav.aero" || site:tav.aero "sevil.arik" || site:tav.aero "@tav.aero" || "TAV" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14584,36 +10918,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>Airport operator contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>"Yalçın Çapanik" "TAV" email || "Yalçın Çapanik" "@tav.aero" || site:tav.aero "yalcin.capanik" || site:tav.aero "@tav.aero" || "TAV" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14699,36 +11003,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Airport operator contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>"Ibrahim Ipekci" "TAV" email || "Ibrahim Ipekci" "@tav.aero" || site:tav.aero "ibrahim.ipekci" || site:tav.aero "@tav.aero" || "TAV" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14814,36 +11088,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Airport operator contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>"Zeynep Samanlioglu" "TAV" email || "Zeynep Samanlioglu" "@tav.aero" || site:tav.aero "zeynep.samanlioglu" || site:tav.aero "@tav.aero" || "TAV" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14929,36 +11173,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Airport operator contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>"Gülten Gür" "TAV" email || "Gülten Gür" "@tav.aero" || site:tav.aero "gulten.gur" || site:tav.aero "@tav.aero" || "TAV" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>https://www.tav.aero/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15044,36 +11258,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>https://www.siemens.com.tr/tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Multinational — siemens.com.tr domain confirmed</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>"Murat Şakacılar" "Siemens Turkey" email || "Murat Şakacılar" "@siemens.com.tr" || site:siemens.com.tr "murat.sakacilar" || site:siemens.com.tr "@siemens.com.tr" || "Siemens Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>https://www.siemens.com.tr/tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15159,36 +11343,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>https://www.mediamarkt.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>"Seçil Namruk" "MediaMarkt Turkey" email || "Seçil Namruk" "@mediamarkt.com.tr" || site:mediamarkt.com.tr "secil.namruk" || site:mediamarkt.com.tr "@mediamarkt.com.tr" || "MediaMarkt Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>https://www.mediamarkt.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15274,36 +11428,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>"Boyner Genc" "Boyner" email || "Boyner Genc" "@boyner.com.tr" || site:boyner.com.tr "boyner.genc" || site:boyner.com.tr "@boyner.com.tr" || "Boyner" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15389,36 +11513,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>"Doruk Can Uyanık" "Boyner" email || "Doruk Can Uyanık" "@boyner.com.tr" || site:boyner.com.tr "doruk.uyanik" || site:boyner.com.tr "@boyner.com.tr" || "Boyner" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15504,36 +11598,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>"Sait Nuri Uludağ" "Boyner" email || "Sait Nuri Uludağ" "@boyner.com.tr" || site:boyner.com.tr "sait.uludag" || site:boyner.com.tr "@boyner.com.tr" || "Boyner" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15619,36 +11683,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>"Duygu Özel" "Boyner" email || "Duygu Özel" "@boyner.com.tr" || site:boyner.com.tr "duygu.ozel" || site:boyner.com.tr "@boyner.com.tr" || "Boyner" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>https://www.boyner.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15734,36 +11768,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>"Selen Erdal" "Defacto" email || "Selen Erdal" "@defacto.com.tr" || site:defacto.com.tr "selen.erdal" || site:defacto.com.tr "@defacto.com.tr" || "Defacto" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15849,36 +11853,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>"Yasemin Hakzade" "Defacto" email || "Yasemin Hakzade" "@defacto.com.tr" || site:defacto.com.tr "yasemin.hakzade" || site:defacto.com.tr "@defacto.com.tr" || "Defacto" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -15964,36 +11938,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>"Yesim Cokeker" "Defacto" email || "Yesim Cokeker" "@defacto.com.tr" || site:defacto.com.tr "yesim.cokeker" || site:defacto.com.tr "@defacto.com.tr" || "Defacto" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16079,36 +12023,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>Retail contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>"İsmail Akkaya" "Defacto" email || "İsmail Akkaya" "@defacto.com.tr" || site:defacto.com.tr "ismail.akkaya" || site:defacto.com.tr "@defacto.com.tr" || "Defacto" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>https://www.defacto.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16194,36 +12108,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>https://www.nestle.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>Multinational — nestle.com.tr domain confirmed</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>"Oğuzhan Besli" "Nestlé Turkey" email || "Oğuzhan Besli" "@nestle.com.tr" || site:nestle.com.tr "oguzhan.besli" || site:nestle.com.tr "@nestle.com.tr" || "Nestlé Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>https://www.nestle.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16309,36 +12193,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>https://www.nestle.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>Multinational — nestle.com.tr domain confirmed</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>"Senem Korol" "Nestlé Turkey" email || "Senem Korol" "@nestle.com.tr" || site:nestle.com.tr "senem.korol" || site:nestle.com.tr "@nestle.com.tr" || "Nestlé Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>https://www.nestle.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16424,36 +12278,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>"Gülçin Özbey" "Borusan" email || "Gülçin Özbey" "@borusan.com" || site:borusan.com "gulcin.ozbey" || site:borusan.com "@borusan.com" || "Borusan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16539,36 +12363,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>"Irem Oner Erdogan" "Borusan" email || "Irem Oner Erdogan" "@borusan.com" || site:borusan.com "irem.erdogan" || site:borusan.com "@borusan.com" || "Borusan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16654,36 +12448,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>"Buket Ekinci" "Borusan" email || "Buket Ekinci" "@borusan.com" || site:borusan.com "buket.ekinci" || site:borusan.com "@borusan.com" || "Borusan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16769,36 +12533,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>"Gürkan Özen" "Borusan" email || "Gürkan Özen" "@borusan.com" || site:borusan.com "gurkan.ozen" || site:borusan.com "@borusan.com" || "Borusan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16884,36 +12618,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>"Elif Arslan Azak" "Borusan" email || "Elif Arslan Azak" "@borusan.com" || site:borusan.com "elif.azak" || site:borusan.com "@borusan.com" || "Borusan" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>https://www.borusan.com/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -16999,36 +12703,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>"Aziz Revnaki" "Yıldız Holding" email || "Aziz Revnaki" "@yildizholding.com.tr" || site:yildizholding.com.tr "aziz.revnaki" || site:yildizholding.com.tr "@yildizholding.com.tr" || "Yıldız Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -17114,36 +12788,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>"Tuncer Konak" "Yıldız Holding" email || "Tuncer Konak" "@yildizholding.com.tr" || site:yildizholding.com.tr "tuncer.konak" || site:yildizholding.com.tr "@yildizholding.com.tr" || "Yıldız Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17229,36 +12873,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>"Merve Koyuncu" "Yıldız Holding" email || "Merve Koyuncu" "@yildizholding.com.tr" || site:yildizholding.com.tr "merve.koyuncu" || site:yildizholding.com.tr "@yildizholding.com.tr" || "Yıldız Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17344,36 +12958,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>"Büşra Altun" "Yıldız Holding" email || "Büşra Altun" "@yildizholding.com.tr" || site:yildizholding.com.tr "busra.altun" || site:yildizholding.com.tr "@yildizholding.com.tr" || "Yıldız Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -17459,36 +13043,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>"Duygu Yılmaz" "Yıldız Holding" email || "Duygu Yılmaz" "@yildizholding.com.tr" || site:yildizholding.com.tr "duygu.yilmaz" || site:yildizholding.com.tr "@yildizholding.com.tr" || "Yıldız Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>https://www.yildizholding.com.tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -17574,36 +13128,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>"Bora Karden" "Zorlu Holding" email || "Bora Karden" "@zorlu.com.tr" || site:zorlu.com.tr "bora.karden" || site:zorlu.com.tr "@zorlu.com.tr" || "Zorlu Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -17689,36 +13213,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>"Elif Kasap" "Zorlu Holding" email || "Elif Kasap" "@zorlu.com.tr" || site:zorlu.com.tr "elif.kasap" || site:zorlu.com.tr "@zorlu.com.tr" || "Zorlu Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -17804,36 +13298,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>"Beste Pınar Sadak" "Zorlu Holding" email || "Beste Pınar Sadak" "@zorlu.com.tr" || site:zorlu.com.tr "beste.sadak" || site:zorlu.com.tr "@zorlu.com.tr" || "Zorlu Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -17919,36 +13383,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>"Sevda Yaşar" "Zorlu Holding" email || "Sevda Yaşar" "@zorlu.com.tr" || site:zorlu.com.tr "sevda.yasar" || site:zorlu.com.tr "@zorlu.com.tr" || "Zorlu Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -18034,36 +13468,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>"Ufuk Karabulut" "Zorlu Holding" email || "Ufuk Karabulut" "@zorlu.com.tr" || site:zorlu.com.tr "ufuk.karabulut" || site:zorlu.com.tr "@zorlu.com.tr" || "Zorlu Holding" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>https://www.zorlu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -18149,36 +13553,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>https://www.dogusgrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>"Merve Öz" "Doğuş" email || "Merve Öz" "@dogusgrubu.com.tr" || site:dogusgrubu.com.tr "merve.oz" || site:dogusgrubu.com.tr "@dogusgrubu.com.tr" || "Doğuş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>https://www.dogusgrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -18264,36 +13638,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>https://www.dogusgrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>"Irem Balcı" "Doğuş" email || "Irem Balcı" "@dogusgrubu.com.tr" || site:dogusgrubu.com.tr "irem.balci" || site:dogusgrubu.com.tr "@dogusgrubu.com.tr" || "Doğuş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>https://www.dogusgrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -18379,36 +13723,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>https://www.dogusgrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>"Buse Küçük" "Doğuş" email || "Buse Küçük" "@dogusgrubu.com.tr" || site:dogusgrubu.com.tr "buse.kucuk" || site:dogusgrubu.com.tr "@dogusgrubu.com.tr" || "Doğuş" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>https://www.dogusgrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -18494,36 +13808,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>https://www.anadolugrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>"Ismail K." "Anadolu" email || "Ismail K." "@anadolugrubu.com.tr" || site:anadolugrubu.com.tr "ismail.k" || site:anadolugrubu.com.tr "@anadolugrubu.com.tr" || "Anadolu" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>https://www.anadolugrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -18609,36 +13893,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>https://www.anadolugrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>"Dr. K. Mehmet Büyükçolak" "Anadolu" email || "Dr. K. Mehmet Büyükçolak" "@anadolugrubu.com.tr" || site:anadolugrubu.com.tr "mehmet.buyukcolak" || site:anadolugrubu.com.tr "@anadolugrubu.com.tr" || "Anadolu" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>https://www.anadolugrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -18724,36 +13978,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>https://www.anadolugrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>Holding contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>"Veysel Akdeniz" "Anadolu" email || "Veysel Akdeniz" "@anadolugrubu.com.tr" || site:anadolugrubu.com.tr "veysel.akdeniz" || site:anadolugrubu.com.tr "@anadolugrubu.com.tr" || "Anadolu" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>https://www.anadolugrubu.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -18839,36 +14063,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>"Selda Beyaz" "Kariyer.net" email || "Selda Beyaz" "@kariyer.net" || site:kariyer.net "selda.beyaz" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -18954,36 +14148,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>"Funda Ceylan Dalkılıç" "Kariyer.net" email || "Funda Ceylan Dalkılıç" "@kariyer.net" || site:kariyer.net "funda.dalkilic" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -19069,36 +14233,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>"Pelin Tuna" "Kariyer.net" email || "Pelin Tuna" "@kariyer.net" || site:kariyer.net "pelin.tuna" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -19184,36 +14318,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>"Nursel Abatay" "Kariyer.net" email || "Nursel Abatay" "@kariyer.net" || site:kariyer.net "nursel.abatay" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19299,36 +14403,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>"Dilek Telhan" "Kariyer.net" email || "Dilek Telhan" "@kariyer.net" || site:kariyer.net "dilek.telhan" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -19414,36 +14488,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>"Burcu Çağlar" "Kariyer.net" email || "Burcu Çağlar" "@kariyer.net" || site:kariyer.net "burcu.caglar" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -19529,36 +14573,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>"Gizem Çapa" "Kariyer.net" email || "Gizem Çapa" "@kariyer.net" || site:kariyer.net "gizem.capa" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -19644,36 +14658,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V167" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>"Merve Çelik" "Kariyer.net" email || "Merve Çelik" "@kariyer.net" || site:kariyer.net "merve.celik" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -19759,36 +14743,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>"Kubilay Batuhan Güzel" "Kariyer.net" email || "Kubilay Batuhan Güzel" "@kariyer.net" || site:kariyer.net "kubilay.guzel" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -19874,36 +14828,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>HR tech company — kariyer.net domain confirmed</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>"Şeyma Çakmakçı" "Kariyer.net" email || "Şeyma Çakmakçı" "@kariyer.net" || site:kariyer.net "seyma.cakmakci" || site:kariyer.net "@kariyer.net" || "Kariyer.net" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>https://www.kariyer.net/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -19989,36 +14913,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>https://www.papara.com/contact?hl=tr_TR</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>Official contact page confirms @papara.com domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>"Neslişah Sultan Türkmen Şen" "Papara" email || "Neslişah Sultan Türkmen Şen" "@papara.com" || site:papara.com "neslisah.sen" || site:papara.com "@papara.com" || "Papara" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>https://www.papara.com/contact?hl=tr_TR</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -20104,36 +14998,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>https://www.papara.com/contact?hl=tr_TR</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>Official contact page confirms @papara.com domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>"Dilara Aydın" "Papara" email || "Dilara Aydın" "@papara.com" || site:papara.com "dilara.aydin" || site:papara.com "@papara.com" || "Papara" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>https://www.papara.com/contact?hl=tr_TR</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -20219,36 +15083,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>https://www.papara.com/contact?hl=tr_TR</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>Official contact page confirms @papara.com domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>"Figen Saltık Yüksek" "Papara" email || "Figen Saltık Yüksek" "@papara.com" || site:papara.com "figen.yuksek" || site:papara.com "@papara.com" || "Papara" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>https://www.papara.com/contact?hl=tr_TR</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -20334,36 +15168,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>https://www.socar.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>Energy company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>"Ilhan Çağlar" "Socar Turkey" email || "Ilhan Çağlar" "@socar.com.tr" || site:socar.com.tr "ilhan.caglar" || site:socar.com.tr "@socar.com.tr" || "Socar Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>https://www.socar.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20449,36 +15253,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>https://www.socar.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>Energy company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>"Burcu Sarpkaya Şakır" "Socar Turkey" email || "Burcu Sarpkaya Şakır" "@socar.com.tr" || site:socar.com.tr "burcu.sakir" || site:socar.com.tr "@socar.com.tr" || "Socar Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>https://www.socar.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -20564,36 +15338,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>https://www.socar.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>Energy company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>"Adnan Kozok" "Socar Turkey" email || "Adnan Kozok" "@socar.com.tr" || site:socar.com.tr "adnan.kozok" || site:socar.com.tr "@socar.com.tr" || "Socar Turkey" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>https://www.socar.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -20679,36 +15423,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>https://www.cci.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>Beverage company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>"Nazan Üstünel" "CCI" email || "Nazan Üstünel" "@cci.com.tr" || site:cci.com.tr "nazan.ustunel" || site:cci.com.tr "@cci.com.tr" || "CCI" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>https://www.cci.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -20794,36 +15508,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>https://www.cci.com.tr/tr/iletisim</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>Beverage company contact page — corporate domain confirmed</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>"Berat Yıldız" "CCI" email || "Berat Yıldız" "@cci.com.tr" || site:cci.com.tr "berat.yildiz" || site:cci.com.tr "@cci.com.tr" || "CCI" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>https://www.cci.com.tr/tr/iletisim</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -20909,36 +15593,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>Official ethics hotline confirms @kale.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>"Sabri Dünya" "Kale" email || "Sabri Dünya" "@kale.com.tr" || site:kale.com.tr "sabri.dunya" || site:kale.com.tr "@kale.com.tr" || "Kale" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -21024,36 +15678,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>Official ethics hotline confirms @kale.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>"Hoya Beri̇k Yanardağ" "Kale" email || "Hoya Beri̇k Yanardağ" "@kale.com.tr" || site:kale.com.tr "hoya.yanardag" || site:kale.com.tr "@kale.com.tr" || "Kale" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -21139,36 +15763,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>Official ethics hotline confirms @kale.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>"Hümeyra Kolancı" "Kale" email || "Hümeyra Kolancı" "@kale.com.tr" || site:kale.com.tr "humeyra.kolanci" || site:kale.com.tr "@kale.com.tr" || "Kale" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -21254,36 +15848,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>Official ethics hotline confirms @kale.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>"Suleyman Sezgin" "Kale" email || "Suleyman Sezgin" "@kale.com.tr" || site:kale.com.tr "suleyman.sezgin" || site:kale.com.tr "@kale.com.tr" || "Kale" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -21369,39 +15933,9 @@
           <t>70</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>Official ethics hotline confirms @kale.com.tr domain; first.last is an inferred pattern</t>
-        </is>
-      </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>first.last</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>Domain evidence found; email pattern is inferred</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>"Beyza Yağmur" "Kale" email || "Beyza Yağmur" "@kale.com.tr" || site:kale.com.tr "beyza.yagmur" || site:kale.com.tr "@kale.com.tr" || "Kale" "email" "human resources"</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>https://www.kale.com.tr/tr-en/ethics-hotline</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y182"/>
+  <autoFilter ref="A1:S182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>